--- a/exports/MANKIND_full_report.xlsx
+++ b/exports/MANKIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1849.9</v>
+        <v>1807.25</v>
       </c>
       <c r="I2" t="n">
         <v>1814.274611281628</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K2" t="n">
-        <v>35.72</v>
+        <v>32.59</v>
       </c>
       <c r="L2" t="n">
         <v>8.859999999999999</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45141.38541666666</v>
+        <v>45141.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1857</v>
+        <v>1913.75</v>
       </c>
       <c r="I3" t="n">
         <v>1883.643174554287</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.75</v>
+        <v>-5.89</v>
       </c>
       <c r="L3" t="n">
         <v>5.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.55</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45170.38541666666</v>
+        <v>45170.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1780.05</v>
+        <v>1717.9</v>
       </c>
       <c r="I4" t="n">
         <v>1756.753307971475</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.99</v>
+        <v>-10.23</v>
       </c>
       <c r="L4" t="n">
-        <v>8.470000000000001</v>
+        <v>11.89</v>
       </c>
       <c r="M4" t="n">
         <v>0.88</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>7.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1765</v>
+        <v>1793.55</v>
       </c>
       <c r="I5" t="n">
         <v>1790.119155086595</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.74</v>
+        <v>-4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.75</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>4.32</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1749</v>
+        <v>1712.05</v>
       </c>
       <c r="I6" t="n">
         <v>1745.561030946983</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.48</v>
+        <v>-4.54</v>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>4.77</v>
       </c>
       <c r="M6" t="n">
         <v>0.91</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1780.25</v>
+        <v>1805.2</v>
       </c>
       <c r="I7" t="n">
         <v>1787.946605239606</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.98</v>
+        <v>-5.44</v>
       </c>
       <c r="L7" t="n">
-        <v>4.22</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.24</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.81</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45259.38541666666</v>
+        <v>45259.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1903.95</v>
+        <v>1891.4</v>
       </c>
       <c r="I8" t="n">
         <v>1896.111264524956</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>5.47</v>
+        <v>4.78</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.67</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45267.38541666666</v>
+        <v>45267.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1990.8</v>
+        <v>1995.5</v>
       </c>
       <c r="I9" t="n">
         <v>1993.04340945509</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.26</v>
+        <v>-5.5</v>
       </c>
       <c r="L9" t="n">
         <v>6.63</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45271.55208333334</v>
+        <v>45272.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1920.05</v>
+        <v>1868</v>
       </c>
       <c r="I10" t="n">
         <v>1869.878369726738</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.78</v>
+        <v>-6.39</v>
       </c>
       <c r="L10" t="n">
-        <v>4.48</v>
+        <v>8.42</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.94</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
         <v>2.28</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.74</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45287.38541666666</v>
+        <v>45287.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1993</v>
+        <v>2004.95</v>
       </c>
       <c r="I11" t="n">
         <v>1996.293772038569</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.69</v>
+        <v>-7.33</v>
       </c>
       <c r="L11" t="n">
         <v>9.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.14</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45315.55208333334</v>
+        <v>45316.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2059.95</v>
+        <v>2030</v>
       </c>
       <c r="I12" t="n">
         <v>2057.175091944278</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.94</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45329.55208333334</v>
+        <v>45330.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2130</v>
+        <v>2273.85</v>
       </c>
       <c r="I13" t="n">
         <v>2164.245542826152</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.93</v>
+        <v>-12.01</v>
       </c>
       <c r="L13" t="n">
-        <v>6.31</v>
+        <v>13.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>5.63</v>
       </c>
       <c r="O13" t="n">
         <v>-1.45</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45348.38541666666</v>
+        <v>45348.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2097.9</v>
+        <v>2074</v>
       </c>
       <c r="I14" t="n">
         <v>2085.913048148663</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.74</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.78</v>
+        <v>10.72</v>
       </c>
       <c r="M14" t="n">
         <v>0.88</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45365.55208333334</v>
+        <v>45366.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2132.75</v>
+        <v>2196.3</v>
       </c>
       <c r="I15" t="n">
         <v>2193.353274514448</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.83</v>
+        <v>-5.9</v>
       </c>
       <c r="L15" t="n">
-        <v>6.79</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
         <v>1.16</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2284.8</v>
+        <v>2202.55</v>
       </c>
       <c r="I16" t="n">
         <v>2255.565830594136</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K16" t="n">
-        <v>4.03</v>
+        <v>0.28</v>
       </c>
       <c r="L16" t="n">
         <v>5.49</v>
@@ -1353,7 +1544,7 @@
         <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.71</v>
+        <v>3.24</v>
       </c>
       <c r="O16" t="n">
         <v>1.32</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2216</v>
+        <v>2242.95</v>
       </c>
       <c r="I17" t="n">
         <v>2221.159498556897</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.61</v>
+        <v>-1.83</v>
       </c>
       <c r="L17" t="n">
         <v>4.57</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45469.55208333334</v>
+        <v>45470.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2149</v>
+        <v>2110</v>
       </c>
       <c r="I18" t="n">
         <v>2119.040132340764</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.19</v>
+        <v>-5.93</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
         <v>0.1</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.71</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2065</v>
+        <v>2093.8</v>
       </c>
       <c r="I19" t="n">
         <v>2080.543635255779</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K19" t="n">
-        <v>2.13</v>
+        <v>0.77</v>
       </c>
       <c r="L19" t="n">
         <v>6.64</v>
@@ -1524,7 +1751,7 @@
         <v>4.63</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>3.63</v>
       </c>
       <c r="O19" t="n">
         <v>-0.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2570</v>
+        <v>2524.5</v>
       </c>
       <c r="I20" t="n">
         <v>2563.711092288744</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K20" t="n">
-        <v>22.74</v>
+        <v>20.57</v>
       </c>
       <c r="L20" t="n">
         <v>2.45</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>8.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2532.9</v>
+        <v>2637</v>
       </c>
       <c r="I21" t="n">
         <v>2599.737593743703</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.33</v>
+        <v>-4.46</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>5.13</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
         <v>4.24</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.85</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2614.75</v>
+        <v>2537.05</v>
       </c>
       <c r="I22" t="n">
         <v>2549.013513288985</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.84</v>
+        <v>-3.79</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>4.97</v>
       </c>
       <c r="M22" t="n">
         <v>0.34</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2664</v>
+        <v>2757.95</v>
       </c>
       <c r="I23" t="n">
         <v>2700.220085019904</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-5</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.5</v>
+        <v>9.58</v>
       </c>
       <c r="M23" t="n">
         <v>1.82</v>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>4.77</v>
       </c>
       <c r="O23" t="n">
         <v>-2.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.34</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>2777.1</v>
+        <v>2740</v>
       </c>
       <c r="I24" t="n">
         <v>2742.448927291123</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="L24" t="n">
         <v>4.78</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.2</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2250</v>
+        <v>2341.6</v>
       </c>
       <c r="I25" t="n">
         <v>2286.555357061678</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>17.88</v>
+        <v>14.54</v>
       </c>
       <c r="L25" t="n">
         <v>1.55</v>
@@ -1866,7 +2165,7 @@
         <v>2.32</v>
       </c>
       <c r="N25" t="n">
-        <v>4.38</v>
+        <v>6.82</v>
       </c>
       <c r="O25" t="n">
         <v>-3.62</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2457.1</v>
+        <v>2381.6</v>
       </c>
       <c r="I26" t="n">
         <v>2437.892242095062</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>4.93</v>
+        <v>1.71</v>
       </c>
       <c r="L26" t="n">
         <v>3.78</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2498</v>
+        <v>2540</v>
       </c>
       <c r="I27" t="n">
         <v>2523.510861177286</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.89</v>
+        <v>-6.65</v>
       </c>
       <c r="L27" t="n">
-        <v>6.16</v>
+        <v>7.69</v>
       </c>
       <c r="M27" t="n">
         <v>2.33</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45810.38541666666</v>
+        <v>45810.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>2446.1</v>
+        <v>2411.3</v>
       </c>
       <c r="I28" t="n">
         <v>2420.385663412207</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.7</v>
+        <v>-5.07</v>
       </c>
       <c r="L28" t="n">
-        <v>5.06</v>
+        <v>5.31</v>
       </c>
       <c r="M28" t="n">
         <v>3.16</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.47</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2282</v>
+        <v>2408.3</v>
       </c>
       <c r="I29" t="n">
         <v>2382.940643735692</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>5.36</v>
+        <v>0.12</v>
       </c>
       <c r="L29" t="n">
         <v>2.02</v>
@@ -2094,7 +2441,7 @@
         <v>2.02</v>
       </c>
       <c r="N29" t="n">
-        <v>1.26</v>
+        <v>4.51</v>
       </c>
       <c r="O29" t="n">
         <v>-2.17</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.85</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45875.55208333334</v>
+        <v>45876.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2550</v>
+        <v>2510.9</v>
       </c>
       <c r="I30" t="n">
         <v>2534.627326487929</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>5.88</v>
+        <v>4.26</v>
       </c>
       <c r="L30" t="n">
         <v>4.99</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.48</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2505</v>
+        <v>2578.4</v>
       </c>
       <c r="I31" t="n">
         <v>2575.551084637605</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>0.23</v>
+        <v>-2.69</v>
       </c>
       <c r="L31" t="n">
-        <v>2.58</v>
+        <v>4.7</v>
       </c>
       <c r="M31" t="n">
         <v>1.15</v>
       </c>
       <c r="N31" t="n">
-        <v>1.85</v>
+        <v>3.84</v>
       </c>
       <c r="O31" t="n">
         <v>-0.76</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.29</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2561.7</v>
+        <v>2544.6</v>
       </c>
       <c r="I32" t="n">
         <v>2553.5613313457</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.65</v>
+        <v>-1.31</v>
       </c>
       <c r="L32" t="n">
         <v>4.78</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2182.1</v>
+        <v>2236.5</v>
       </c>
       <c r="I33" t="n">
         <v>2189.241497450913</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K33" t="n">
-        <v>14.25</v>
+        <v>12.11</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2250</v>
+        <v>2196.9</v>
       </c>
       <c r="I34" t="n">
         <v>2206.127703703641</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>-1.77</v>
       </c>
       <c r="L34" t="n">
         <v>4.04</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.06</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46077.55208333334</v>
+        <v>46078.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2060</v>
+        <v>2114</v>
       </c>
       <c r="I35" t="n">
         <v>2111.145268605113</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K35" t="n">
-        <v>6.23</v>
+        <v>3.77</v>
       </c>
       <c r="L35" t="n">
         <v>2.67</v>
@@ -2436,7 +2855,7 @@
         <v>2.59</v>
       </c>
       <c r="N35" t="n">
-        <v>3.97</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
         <v>-2.15</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.7</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2182</v>
+        <v>2138.5</v>
       </c>
       <c r="I36" t="n">
         <v>2150.398413758857</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>3.22</v>
+        <v>1.16</v>
       </c>
       <c r="L36" t="n">
         <v>2.89</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2045</v>
+        <v>2069.5</v>
       </c>
       <c r="I37" t="n">
         <v>2064.024510252932</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K37" t="n">
-        <v>4.37</v>
+        <v>3.23</v>
       </c>
       <c r="L37" t="n">
         <v>5.53</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.26</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2428.4</v>
+        <v>2400</v>
       </c>
       <c r="I38" t="n">
         <v>2404.659024849991</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>17.34</v>
+        <v>15.97</v>
       </c>
       <c r="L38" t="n">
         <v>2.65</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.75</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46192.55208333334</v>
+        <v>46195.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2418</v>
+        <v>2459.9</v>
       </c>
       <c r="I39" t="n">
         <v>2438.096642937865</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.75</v>
+        <v>-2.5</v>
       </c>
       <c r="L39" t="n">
         <v>2.87</v>
@@ -2664,7 +3131,7 @@
         <v>1.85</v>
       </c>
       <c r="N39" t="n">
-        <v>3.51</v>
+        <v>5.05</v>
       </c>
       <c r="O39" t="n">
         <v>-0.8</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.65</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2569.9</v>
+        <v>2475.1</v>
       </c>
       <c r="I40" t="n">
         <v>2495.137311307999</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K40" t="n">
-        <v>4.47</v>
+        <v>0.62</v>
       </c>
       <c r="L40" t="n">
         <v>2.27</v>
@@ -2721,7 +3200,7 @@
         <v>0.55</v>
       </c>
       <c r="N40" t="n">
-        <v>2.84</v>
+        <v>3.81</v>
       </c>
       <c r="O40" t="n">
         <v>5.05</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2315.1</v>
+        <v>2439.5</v>
       </c>
       <c r="I41" t="n">
         <v>2334.981122845863</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K41" t="n">
-        <v>6.46</v>
+        <v>1.44</v>
       </c>
       <c r="L41" t="n">
         <v>5.59</v>
@@ -2778,7 +3269,7 @@
         <v>1.55</v>
       </c>
       <c r="N41" t="n">
-        <v>2.26</v>
+        <v>5.01</v>
       </c>
       <c r="O41" t="n">
         <v>-3.81</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.98</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2500</v>
+        <v>2392</v>
       </c>
       <c r="I42" t="n">
         <v>2419.430156693326</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>2.48</v>
+        <v>-1.95</v>
       </c>
       <c r="L42" t="n">
         <v>5.6</v>
@@ -2835,7 +3338,7 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>2.04</v>
+        <v>5.28</v>
       </c>
       <c r="O42" t="n">
         <v>5.01</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2310</v>
+        <v>2514</v>
       </c>
       <c r="I43" t="n">
         <v>2348.217963471253</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>3.43</v>
+        <v>-5.1</v>
       </c>
       <c r="L43" t="n">
-        <v>4.97</v>
+        <v>5.39</v>
       </c>
       <c r="M43" t="n">
-        <v>0.72</v>
+        <v>2.1</v>
       </c>
       <c r="N43" t="n">
-        <v>4.62</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>-5.28</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2952,6 +3479,12 @@
       <c r="Q44" t="n">
         <v>2</v>
       </c>
+      <c r="R44" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4510,7 +5043,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -4520,7 +5053,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="7">
@@ -4530,7 +5063,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89.2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -4540,7 +5073,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -4550,7 +5083,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
@@ -4560,7 +5093,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="11">
@@ -4600,7 +5133,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.37</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15">
@@ -4610,7 +5143,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.81</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="16">
@@ -4620,7 +5153,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.93</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="17">
@@ -4630,7 +5163,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.72</v>
+        <v>32.59</v>
       </c>
     </row>
     <row r="18">
@@ -4640,7 +5173,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.4</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="19">
@@ -4650,7 +5183,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.75</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="20">
@@ -4660,7 +5193,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.78</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="21">
@@ -4670,7 +5203,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.16</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="22">
@@ -4680,7 +5213,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4690,7 +5223,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4700,7 +5233,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="25">
@@ -4720,7 +5253,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="27">
@@ -4740,7 +5273,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
